--- a/research/traditional_assets/database/data/thailand/thailand_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0235</v>
+        <v>0.111175</v>
       </c>
       <c r="E2">
-        <v>-0.165</v>
+        <v>0.0664</v>
       </c>
       <c r="G2">
-        <v>0.1583762886597938</v>
+        <v>-0.3305358362788487</v>
       </c>
       <c r="H2">
-        <v>0.1583762886597938</v>
+        <v>-0.3305358362788487</v>
       </c>
       <c r="I2">
-        <v>-0.2077030750088873</v>
+        <v>-0.001381786239303546</v>
       </c>
       <c r="J2">
-        <v>-0.1832865508029003</v>
+        <v>-0.001200048970365818</v>
       </c>
       <c r="K2">
-        <v>25.142</v>
+        <v>-18.202</v>
       </c>
       <c r="L2">
-        <v>0.02793059011731248</v>
+        <v>-0.02703240561974634</v>
       </c>
       <c r="M2">
-        <v>38.332</v>
+        <v>30.497</v>
       </c>
       <c r="N2">
-        <v>0.02470163680886712</v>
+        <v>0.0221265326851919</v>
       </c>
       <c r="O2">
-        <v>1.524620157505369</v>
+        <v>-1.675475222503022</v>
       </c>
       <c r="P2">
-        <v>38.332</v>
+        <v>22.387</v>
       </c>
       <c r="Q2">
-        <v>0.02470163680886712</v>
+        <v>0.0162424726111877</v>
       </c>
       <c r="R2">
-        <v>1.524620157505369</v>
+        <v>-1.229919789034172</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.2659277961766731</v>
       </c>
       <c r="U2">
-        <v>203.55</v>
+        <v>96.45</v>
       </c>
       <c r="V2">
-        <v>0.1311702538986983</v>
+        <v>0.06997750852499457</v>
       </c>
       <c r="W2">
-        <v>0.203781106262531</v>
+        <v>0.04242424242424243</v>
       </c>
       <c r="X2">
-        <v>0.05739173692414451</v>
+        <v>0.1055243251428911</v>
       </c>
       <c r="Y2">
-        <v>0.1463893693383864</v>
+        <v>-0.06310008271864873</v>
       </c>
       <c r="Z2">
-        <v>0.9917588471200035</v>
+        <v>0.7275048771642912</v>
       </c>
       <c r="AA2">
-        <v>0.209459221502754</v>
+        <v>0.05569482826687722</v>
       </c>
       <c r="AB2">
-        <v>0.05561368878193921</v>
+        <v>0.09399768240568446</v>
       </c>
       <c r="AC2">
-        <v>0.1538455327208147</v>
+        <v>-0.03867104711416166</v>
       </c>
       <c r="AD2">
-        <v>499.865</v>
+        <v>606.651</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.222059731863246</v>
       </c>
       <c r="AF2">
-        <v>499.865</v>
+        <v>607.8730597318632</v>
       </c>
       <c r="AG2">
-        <v>296.315</v>
+        <v>511.4230597318632</v>
       </c>
       <c r="AH2">
-        <v>0.2436387031995964</v>
+        <v>0.3060524140902038</v>
       </c>
       <c r="AI2">
-        <v>0.5145952901814438</v>
+        <v>0.6075674170299633</v>
       </c>
       <c r="AJ2">
-        <v>0.1603336372465999</v>
+        <v>0.2706338672738799</v>
       </c>
       <c r="AK2">
-        <v>0.385914759222479</v>
+        <v>0.5657002697203949</v>
       </c>
       <c r="AL2">
-        <v>13.017</v>
+        <v>16.874</v>
       </c>
       <c r="AM2">
-        <v>12.192</v>
+        <v>16.238</v>
       </c>
       <c r="AN2">
-        <v>-3.754798049982348</v>
+        <v>11.94900531810124</v>
       </c>
       <c r="AO2">
-        <v>-14.3632173311823</v>
+        <v>-0.0932203389830509</v>
       </c>
       <c r="AP2">
-        <v>-2.225806936233822</v>
+        <v>10.07333188362937</v>
       </c>
       <c r="AQ2">
-        <v>-15.33513779527559</v>
+        <v>-0.09687153590343643</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TQR Public Company Limited (SET:TQR)</t>
+          <t>TQM Alpha Public Company Limited (SET:TQM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,115 +722,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5169628432956381</v>
+        <v>0.3553072625698324</v>
       </c>
       <c r="H3">
-        <v>0.5169628432956381</v>
+        <v>0.3553072625698324</v>
       </c>
       <c r="I3">
-        <v>0.4636510500807755</v>
+        <v>0.2782122905027933</v>
       </c>
       <c r="J3">
-        <v>0.3883236329032687</v>
+        <v>0.2206288164219826</v>
       </c>
       <c r="K3">
-        <v>3.06</v>
+        <v>20.1</v>
       </c>
       <c r="L3">
-        <v>0.494345718901454</v>
+        <v>0.2245810055865922</v>
       </c>
       <c r="M3">
-        <v>1.68</v>
+        <v>28.31</v>
       </c>
       <c r="N3">
-        <v>0.01703853955375254</v>
+        <v>0.04182301669375092</v>
       </c>
       <c r="O3">
-        <v>0.5490196078431372</v>
+        <v>1.408457711442786</v>
       </c>
       <c r="P3">
-        <v>1.68</v>
+        <v>20.2</v>
       </c>
       <c r="Q3">
-        <v>0.01703853955375254</v>
+        <v>0.02984192642931009</v>
       </c>
       <c r="R3">
-        <v>0.5490196078431372</v>
+        <v>1.004975124378109</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.286471211586012</v>
       </c>
       <c r="U3">
-        <v>4.34</v>
+        <v>16.1</v>
       </c>
       <c r="V3">
-        <v>0.04401622718052738</v>
+        <v>0.02378490175801448</v>
       </c>
       <c r="W3">
-        <v>0.8793103448275862</v>
+        <v>0.291304347826087</v>
       </c>
       <c r="X3">
-        <v>0.05529257342739465</v>
+        <v>0.09297534022063106</v>
       </c>
       <c r="Y3">
-        <v>0.8240177714001915</v>
+        <v>0.1983290076054559</v>
       </c>
       <c r="Z3">
-        <v>15.95360824742269</v>
+        <v>1.278571428571428</v>
       </c>
       <c r="AA3">
-        <v>6.195163112554726</v>
+        <v>0.2820897009966777</v>
       </c>
       <c r="AB3">
-        <v>0.05520839042935049</v>
+        <v>0.09198015116598084</v>
       </c>
       <c r="AC3">
-        <v>6.139954722125375</v>
+        <v>0.1901095498306968</v>
       </c>
       <c r="AD3">
-        <v>0.425</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.425</v>
+        <v>17.5</v>
       </c>
       <c r="AG3">
-        <v>-3.915</v>
+        <v>1.399999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.004291845493562232</v>
+        <v>0.02520161290322581</v>
       </c>
       <c r="AI3">
-        <v>0.0303030303030303</v>
+        <v>0.1883745963401507</v>
       </c>
       <c r="AJ3">
-        <v>-0.04134762633996938</v>
+        <v>0.002063983488132093</v>
       </c>
       <c r="AK3">
-        <v>-0.4042333505420754</v>
+        <v>0.01822916666666665</v>
       </c>
       <c r="AL3">
-        <v>0.021</v>
+        <v>0.075</v>
       </c>
       <c r="AM3">
-        <v>0.021</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.150709219858156</v>
+        <v>0.6294964028776978</v>
       </c>
       <c r="AO3">
-        <v>136.6666666666667</v>
+        <v>332</v>
       </c>
       <c r="AP3">
-        <v>-1.388297872340426</v>
+        <v>0.05035971223021578</v>
       </c>
       <c r="AQ3">
-        <v>136.6666666666667</v>
+        <v>-44.38502673796791</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TQM Corporation Public Company Limited (SET:TQM)</t>
+          <t>TQR Public Company Limited (SET:TQR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,40 +850,40 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.2985537190082644</v>
+        <v>0.5341959334565619</v>
       </c>
       <c r="H4">
-        <v>0.2985537190082644</v>
+        <v>0.5341959334565619</v>
       </c>
       <c r="I4">
-        <v>0.2964876033057851</v>
+        <v>0.3290203327171904</v>
       </c>
       <c r="J4">
-        <v>0.2410737860745122</v>
+        <v>0.2484899528948781</v>
       </c>
       <c r="K4">
-        <v>25.5</v>
+        <v>1.87</v>
       </c>
       <c r="L4">
-        <v>0.2634297520661157</v>
+        <v>0.3456561922365989</v>
       </c>
       <c r="M4">
-        <v>23.2</v>
+        <v>1.79</v>
       </c>
       <c r="N4">
-        <v>0.02659025787965616</v>
+        <v>0.02300771208226221</v>
       </c>
       <c r="O4">
-        <v>0.9098039215686274</v>
+        <v>0.9572192513368983</v>
       </c>
       <c r="P4">
-        <v>23.2</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>0.02659025787965616</v>
+        <v>0.02300771208226221</v>
       </c>
       <c r="R4">
-        <v>0.9098039215686274</v>
+        <v>0.9572192513368983</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,73 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>14.5</v>
+        <v>1.47</v>
       </c>
       <c r="V4">
-        <v>0.0166189111747851</v>
+        <v>0.01889460154241645</v>
       </c>
       <c r="W4">
-        <v>0.3669064748201439</v>
+        <v>0.1375</v>
       </c>
       <c r="X4">
-        <v>0.05572370990463255</v>
+        <v>0.09203638565167616</v>
       </c>
       <c r="Y4">
-        <v>0.3111827649155113</v>
+        <v>0.04546361434832386</v>
       </c>
       <c r="Z4">
-        <v>1.43620178041543</v>
+        <v>0.5585957666494579</v>
       </c>
       <c r="AA4">
-        <v>0.3462306007717029</v>
+        <v>0.1388054357420021</v>
       </c>
       <c r="AB4">
-        <v>0.0553738118045946</v>
+        <v>0.09191568630332879</v>
       </c>
       <c r="AC4">
-        <v>0.2908567889671083</v>
+        <v>0.04688974943867331</v>
       </c>
       <c r="AD4">
-        <v>15.5</v>
+        <v>0.291</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>0.291</v>
       </c>
       <c r="AG4">
-        <v>1</v>
+        <v>-1.179</v>
       </c>
       <c r="AH4">
-        <v>0.01745495495495495</v>
+        <v>0.0037264217387407</v>
       </c>
       <c r="AI4">
-        <v>0.1650692225772098</v>
+        <v>0.02292963517453313</v>
       </c>
       <c r="AJ4">
-        <v>0.001144819690898683</v>
+        <v>-0.01538742642356534</v>
       </c>
       <c r="AK4">
-        <v>0.01259445843828715</v>
+        <v>-0.1050708493004189</v>
       </c>
       <c r="AL4">
-        <v>0.054</v>
+        <v>0.019</v>
       </c>
       <c r="AM4">
-        <v>-0.7709999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="AN4">
-        <v>0.5201342281879194</v>
+        <v>0.1682080924855491</v>
       </c>
       <c r="AO4">
-        <v>531.4814814814815</v>
+        <v>93.68421052631579</v>
       </c>
       <c r="AP4">
-        <v>0.03355704697986577</v>
+        <v>-0.6815028901734105</v>
       </c>
       <c r="AQ4">
-        <v>-37.22438391699092</v>
+        <v>93.68421052631579</v>
       </c>
     </row>
     <row r="5">
@@ -978,46 +978,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0235</v>
+        <v>0.00635</v>
       </c>
       <c r="E5">
-        <v>-0.165</v>
+        <v>0.0664</v>
       </c>
       <c r="G5">
-        <v>0.1748283752860412</v>
+        <v>0.2101736972704714</v>
       </c>
       <c r="H5">
-        <v>0.1748283752860412</v>
+        <v>0.2101736972704714</v>
       </c>
       <c r="I5">
-        <v>0.1061784897025172</v>
+        <v>0.1555831265508685</v>
       </c>
       <c r="J5">
-        <v>0.09334649213183382</v>
+        <v>0.1235513063786308</v>
       </c>
       <c r="K5">
-        <v>0.372</v>
+        <v>0.378</v>
       </c>
       <c r="L5">
-        <v>0.08512585812356979</v>
+        <v>0.09379652605459056</v>
       </c>
       <c r="M5">
-        <v>0.052</v>
+        <v>0.397</v>
       </c>
       <c r="N5">
-        <v>0.002708333333333333</v>
+        <v>0.02294797687861272</v>
       </c>
       <c r="O5">
-        <v>0.1397849462365591</v>
+        <v>1.05026455026455</v>
       </c>
       <c r="P5">
-        <v>0.052</v>
+        <v>0.397</v>
       </c>
       <c r="Q5">
-        <v>0.002708333333333333</v>
+        <v>0.02294797687861272</v>
       </c>
       <c r="R5">
-        <v>0.1397849462365591</v>
+        <v>1.05026455026455</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,73 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>0.1203125</v>
+        <v>0.1433526011560693</v>
       </c>
       <c r="W5">
-        <v>0.04065573770491803</v>
+        <v>0.04242424242424243</v>
       </c>
       <c r="X5">
-        <v>0.05905976394365647</v>
+        <v>0.1055243251428911</v>
       </c>
       <c r="Y5">
-        <v>-0.01840402623873844</v>
+        <v>-0.06310008271864873</v>
       </c>
       <c r="Z5">
-        <v>0.7786885245901639</v>
+        <v>0.4507829977628636</v>
       </c>
       <c r="AA5">
-        <v>0.07268784223380502</v>
+        <v>0.05569482826687722</v>
       </c>
       <c r="AB5">
-        <v>0.05585356575928382</v>
+        <v>0.09436587538103888</v>
       </c>
       <c r="AC5">
-        <v>0.0168342764745212</v>
+        <v>-0.03867104711416166</v>
       </c>
       <c r="AD5">
-        <v>2.34</v>
+        <v>5.56</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.34</v>
+        <v>5.56</v>
       </c>
       <c r="AG5">
-        <v>0.0299999999999998</v>
+        <v>3.08</v>
       </c>
       <c r="AH5">
-        <v>0.1086350974930362</v>
+        <v>0.2432195975503062</v>
       </c>
       <c r="AI5">
-        <v>0.208</v>
+        <v>0.4152352501867064</v>
       </c>
       <c r="AJ5">
-        <v>0.00156006240249609</v>
+        <v>0.1511285574092247</v>
       </c>
       <c r="AK5">
-        <v>0.003355704697986555</v>
+        <v>0.2823098075160403</v>
       </c>
       <c r="AL5">
-        <v>0.042</v>
+        <v>0.15</v>
       </c>
       <c r="AM5">
-        <v>0.042</v>
+        <v>0.15</v>
       </c>
       <c r="AN5">
-        <v>4.231464737793851</v>
+        <v>7.192755498059507</v>
       </c>
       <c r="AO5">
-        <v>11.04761904761905</v>
+        <v>4.180000000000001</v>
       </c>
       <c r="AP5">
-        <v>0.05424954792043364</v>
+        <v>3.984476067270375</v>
       </c>
       <c r="AQ5">
-        <v>11.04761904761905</v>
+        <v>4.180000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thai Group Holdings Public Company Limited (SET:TGH)</t>
+          <t>KWI Public Company Limited (SET:KWI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1111,116 +1111,241 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.216</v>
+      </c>
       <c r="G6">
-        <v>0.1383703329969728</v>
+        <v>-0.4658634538152611</v>
       </c>
       <c r="H6">
-        <v>0.1383703329969728</v>
+        <v>-0.4658634538152611</v>
       </c>
       <c r="I6">
-        <v>-0.2762361251261352</v>
+        <v>-0.07126948518430253</v>
       </c>
       <c r="J6">
-        <v>-0.2762361251261352</v>
+        <v>-0.07126948518430253</v>
       </c>
       <c r="K6">
-        <v>-3.79</v>
+        <v>-3.65</v>
       </c>
       <c r="L6">
-        <v>-0.004780524722502523</v>
+        <v>-0.1465863453815261</v>
       </c>
       <c r="M6">
-        <v>13.4</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.0238646482635797</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-3.535620052770449</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>13.4</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.0238646482635797</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-3.535620052770449</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
+      <c r="U6">
+        <v>12.1</v>
+      </c>
+      <c r="V6">
+        <v>0.07254196642685851</v>
+      </c>
+      <c r="W6">
+        <v>-0.07005758157389635</v>
+      </c>
+      <c r="X6">
+        <v>0.119072634378464</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1891302159523604</v>
+      </c>
+      <c r="Z6">
+        <v>0.144491856486338</v>
+      </c>
+      <c r="AA6">
+        <v>-0.01029786022510543</v>
+      </c>
+      <c r="AB6">
+        <v>0.09587177459967181</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1061696348247772</v>
+      </c>
+      <c r="AD6">
+        <v>106.1</v>
+      </c>
+      <c r="AE6">
+        <v>0.7280509054456642</v>
+      </c>
+      <c r="AF6">
+        <v>106.8280509054457</v>
+      </c>
+      <c r="AG6">
+        <v>94.72805090544567</v>
+      </c>
+      <c r="AH6">
+        <v>0.3904133752075036</v>
+      </c>
+      <c r="AI6">
+        <v>0.5980474531516533</v>
+      </c>
+      <c r="AJ6">
+        <v>0.3622099066524003</v>
+      </c>
+      <c r="AK6">
+        <v>0.5688414077411624</v>
+      </c>
+      <c r="AL6">
+        <v>3.73</v>
+      </c>
+      <c r="AM6">
+        <v>3.73</v>
+      </c>
+      <c r="AN6">
+        <v>-67.62268961121734</v>
+      </c>
+      <c r="AO6">
+        <v>-0.5844504021447722</v>
+      </c>
+      <c r="AP6">
+        <v>-60.3747934387799</v>
+      </c>
+      <c r="AQ6">
+        <v>-0.5844504021447722</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Thai Group Holdings Public Company Limited (SET:TGH)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>-0.448589626933576</v>
+      </c>
+      <c r="H7">
+        <v>-0.448589626933576</v>
+      </c>
+      <c r="I7">
+        <v>-0.04815796499596636</v>
+      </c>
+      <c r="J7">
+        <v>-0.04815796499596636</v>
+      </c>
+      <c r="K7">
+        <v>-36.9</v>
+      </c>
+      <c r="L7">
+        <v>-0.06715195632393084</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
         <v>0</v>
       </c>
-      <c r="U6">
-        <v>182.4</v>
-      </c>
-      <c r="V6">
-        <v>0.3248441674087266</v>
-      </c>
-      <c r="W6">
-        <v>-0.009077844311377245</v>
-      </c>
-      <c r="X6">
-        <v>0.08263830194759818</v>
-      </c>
-      <c r="Y6">
-        <v>-0.09171614625897542</v>
-      </c>
-      <c r="Z6">
-        <v>0.9503260452627541</v>
-      </c>
-      <c r="AA6">
-        <v>-0.2625143843498274</v>
-      </c>
-      <c r="AB6">
-        <v>0.06095666760931746</v>
-      </c>
-      <c r="AC6">
-        <v>-0.3234710519591448</v>
-      </c>
-      <c r="AD6">
-        <v>481.6</v>
-      </c>
-      <c r="AE6">
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
         <v>0</v>
       </c>
-      <c r="AF6">
-        <v>481.6</v>
-      </c>
-      <c r="AG6">
-        <v>299.2</v>
-      </c>
-      <c r="AH6">
-        <v>0.4617006998370243</v>
-      </c>
-      <c r="AI6">
-        <v>0.5651255573808965</v>
-      </c>
-      <c r="AJ6">
-        <v>0.3476240269548043</v>
-      </c>
-      <c r="AK6">
-        <v>0.4467005076142132</v>
-      </c>
-      <c r="AL6">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>64.3</v>
+      </c>
+      <c r="V7">
+        <v>0.1463026166097838</v>
+      </c>
+      <c r="W7">
+        <v>-0.101123595505618</v>
+      </c>
+      <c r="X7">
+        <v>0.1380297052209613</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2391533007265792</v>
+      </c>
+      <c r="Z7">
+        <v>0.8268205742184497</v>
+      </c>
+      <c r="AA7">
+        <v>-0.0398179962711569</v>
+      </c>
+      <c r="AB7">
+        <v>0.09399768240568446</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1338156786768414</v>
+      </c>
+      <c r="AD7">
+        <v>477.2</v>
+      </c>
+      <c r="AE7">
+        <v>0.4940088264175815</v>
+      </c>
+      <c r="AF7">
+        <v>477.6940088264176</v>
+      </c>
+      <c r="AG7">
+        <v>413.3940088264176</v>
+      </c>
+      <c r="AH7">
+        <v>0.5208211177018526</v>
+      </c>
+      <c r="AI7">
+        <v>0.6796103008816312</v>
+      </c>
+      <c r="AJ7">
+        <v>0.4846956416017599</v>
+      </c>
+      <c r="AK7">
+        <v>0.6473502775043826</v>
+      </c>
+      <c r="AL7">
         <v>12.9</v>
       </c>
-      <c r="AM6">
+      <c r="AM7">
         <v>12.9</v>
       </c>
-      <c r="AN6">
-        <v>-2.895971136500301</v>
-      </c>
-      <c r="AO6">
-        <v>-16.97674418604651</v>
-      </c>
-      <c r="AP6">
-        <v>-1.799158147925436</v>
-      </c>
-      <c r="AQ6">
-        <v>-16.97674418604651</v>
+      <c r="AN7">
+        <v>21.65547286258849</v>
+      </c>
+      <c r="AO7">
+        <v>-2.069767441860465</v>
+      </c>
+      <c r="AP7">
+        <v>18.75993868335531</v>
+      </c>
+      <c r="AQ7">
+        <v>-2.069767441860465</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_insurance_general.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111175</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0664</v>
+        <v>0.195</v>
+      </c>
+      <c r="F2">
+        <v>0.15</v>
       </c>
       <c r="G2">
-        <v>-0.3305358362788487</v>
+        <v>0.193366519115956</v>
       </c>
       <c r="H2">
-        <v>-0.3305358362788487</v>
+        <v>0.193366519115956</v>
       </c>
       <c r="I2">
-        <v>-0.001381786239303546</v>
+        <v>0.05792815976666577</v>
       </c>
       <c r="J2">
-        <v>-0.001200048970365818</v>
+        <v>0.04311544274234613</v>
       </c>
       <c r="K2">
-        <v>-18.202</v>
+        <v>4.197000000000003</v>
       </c>
       <c r="L2">
-        <v>-0.02703240561974634</v>
+        <v>0.006611427041161928</v>
       </c>
       <c r="M2">
-        <v>30.497</v>
+        <v>21.407</v>
       </c>
       <c r="N2">
-        <v>0.0221265326851919</v>
+        <v>0.02259790984904465</v>
       </c>
       <c r="O2">
-        <v>-1.675475222503022</v>
+        <v>5.100548010483675</v>
       </c>
       <c r="P2">
-        <v>22.387</v>
+        <v>21.407</v>
       </c>
       <c r="Q2">
-        <v>0.0162424726111877</v>
+        <v>0.02259790984904465</v>
       </c>
       <c r="R2">
-        <v>-1.229919789034172</v>
+        <v>5.100548010483675</v>
       </c>
       <c r="S2">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2659277961766731</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>96.45</v>
+        <v>110.409</v>
       </c>
       <c r="V2">
-        <v>0.06997750852499457</v>
+        <v>0.1165512509236778</v>
       </c>
       <c r="W2">
-        <v>0.04242424242424243</v>
+        <v>0.005123513266239708</v>
       </c>
       <c r="X2">
-        <v>0.1055243251428911</v>
+        <v>0.1007879713442776</v>
       </c>
       <c r="Y2">
-        <v>-0.06310008271864873</v>
+        <v>-0.09566445807803788</v>
       </c>
       <c r="Z2">
-        <v>0.7275048771642912</v>
+        <v>0.735458082487381</v>
       </c>
       <c r="AA2">
-        <v>0.05569482826687722</v>
+        <v>0.0195363571247358</v>
       </c>
       <c r="AB2">
-        <v>0.09399768240568446</v>
+        <v>0.08349281648378155</v>
       </c>
       <c r="AC2">
-        <v>-0.03867104711416166</v>
+        <v>-0.06395645935904576</v>
       </c>
       <c r="AD2">
-        <v>606.651</v>
+        <v>673.552</v>
       </c>
       <c r="AE2">
-        <v>1.222059731863246</v>
+        <v>0.8181244926145306</v>
       </c>
       <c r="AF2">
-        <v>607.8730597318632</v>
+        <v>674.3701244926145</v>
       </c>
       <c r="AG2">
-        <v>511.4230597318632</v>
+        <v>563.9611244926145</v>
       </c>
       <c r="AH2">
-        <v>0.3060524140902038</v>
+        <v>0.4158491386795514</v>
       </c>
       <c r="AI2">
-        <v>0.6075674170299633</v>
+        <v>0.6400687599623963</v>
       </c>
       <c r="AJ2">
-        <v>0.2706338672738799</v>
+        <v>0.3731725215137502</v>
       </c>
       <c r="AK2">
-        <v>0.5657002697203949</v>
+        <v>0.5979351259769942</v>
       </c>
       <c r="AL2">
-        <v>16.874</v>
+        <v>21.788</v>
       </c>
       <c r="AM2">
-        <v>16.238</v>
+        <v>21.043</v>
       </c>
       <c r="AN2">
-        <v>11.94900531810124</v>
+        <v>7.379531734466929</v>
       </c>
       <c r="AO2">
-        <v>-0.0932203389830509</v>
+        <v>1.666375986781715</v>
       </c>
       <c r="AP2">
-        <v>10.07333188362937</v>
+        <v>6.178838478987374</v>
       </c>
       <c r="AQ2">
-        <v>-0.09687153590343643</v>
+        <v>1.725371857624864</v>
       </c>
     </row>
     <row r="3">
@@ -721,116 +724,125 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.195</v>
+      </c>
+      <c r="F3">
+        <v>0.15</v>
+      </c>
       <c r="G3">
-        <v>0.3553072625698324</v>
+        <v>0.3300876338851022</v>
       </c>
       <c r="H3">
-        <v>0.3553072625698324</v>
+        <v>0.3300876338851022</v>
       </c>
       <c r="I3">
-        <v>0.2782122905027933</v>
+        <v>0.2775073028237585</v>
       </c>
       <c r="J3">
-        <v>0.2206288164219826</v>
+        <v>0.2191932682439011</v>
       </c>
       <c r="K3">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="L3">
-        <v>0.2245810055865922</v>
+        <v>0.2151898734177215</v>
       </c>
       <c r="M3">
-        <v>28.31</v>
+        <v>18.6</v>
       </c>
       <c r="N3">
-        <v>0.04182301669375092</v>
+        <v>0.03686087990487515</v>
       </c>
       <c r="O3">
-        <v>1.408457711442786</v>
+        <v>0.8416289592760181</v>
       </c>
       <c r="P3">
-        <v>20.2</v>
+        <v>18.6</v>
       </c>
       <c r="Q3">
-        <v>0.02984192642931009</v>
+        <v>0.03686087990487515</v>
       </c>
       <c r="R3">
-        <v>1.004975124378109</v>
+        <v>0.8416289592760181</v>
       </c>
       <c r="S3">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.286471211586012</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>16.1</v>
+        <v>19.6</v>
       </c>
       <c r="V3">
-        <v>0.02378490175801448</v>
+        <v>0.03884264764169639</v>
       </c>
       <c r="W3">
-        <v>0.291304347826087</v>
+        <v>0.3640856672158155</v>
       </c>
       <c r="X3">
-        <v>0.09297534022063106</v>
+        <v>0.08418341139095517</v>
       </c>
       <c r="Y3">
-        <v>0.1983290076054559</v>
+        <v>0.2799022558248603</v>
       </c>
       <c r="Z3">
-        <v>1.278571428571428</v>
+        <v>1.65378421900161</v>
       </c>
       <c r="AA3">
-        <v>0.2820897009966777</v>
+        <v>0.3624983679331505</v>
       </c>
       <c r="AB3">
-        <v>0.09198015116598084</v>
+        <v>0.0821368494276716</v>
       </c>
       <c r="AC3">
-        <v>0.1901095498306968</v>
+        <v>0.280361518505479</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>32.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.5</v>
+        <v>32.1</v>
       </c>
       <c r="AG3">
-        <v>1.399999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>0.02520161290322581</v>
+        <v>0.05980994969256568</v>
       </c>
       <c r="AI3">
-        <v>0.1883745963401507</v>
+        <v>0.2760103181427343</v>
       </c>
       <c r="AJ3">
-        <v>0.002063983488132093</v>
+        <v>0.02417327402823438</v>
       </c>
       <c r="AK3">
-        <v>0.01822916666666665</v>
+        <v>0.1292657704239917</v>
       </c>
       <c r="AL3">
-        <v>0.075</v>
+        <v>0.309</v>
       </c>
       <c r="AM3">
-        <v>-0.5610000000000001</v>
+        <v>-0.436</v>
       </c>
       <c r="AN3">
-        <v>0.6294964028776978</v>
+        <v>1.015822784810127</v>
       </c>
       <c r="AO3">
-        <v>332</v>
+        <v>92.23300970873787</v>
       </c>
       <c r="AP3">
-        <v>0.05035971223021578</v>
+        <v>0.3955696202531646</v>
       </c>
       <c r="AQ3">
-        <v>-44.38502673796791</v>
+        <v>-65.36697247706422</v>
       </c>
     </row>
     <row r="4">
@@ -850,40 +862,40 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.5341959334565619</v>
+        <v>0.5230547550432276</v>
       </c>
       <c r="H4">
-        <v>0.5341959334565619</v>
+        <v>0.5230547550432276</v>
       </c>
       <c r="I4">
-        <v>0.3290203327171904</v>
+        <v>0.5043227665706052</v>
       </c>
       <c r="J4">
-        <v>0.2484899528948781</v>
+        <v>0.4015299203254789</v>
       </c>
       <c r="K4">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="L4">
-        <v>0.3456561922365989</v>
+        <v>0.3890489913544669</v>
       </c>
       <c r="M4">
-        <v>1.79</v>
+        <v>2.67</v>
       </c>
       <c r="N4">
-        <v>0.02300771208226221</v>
+        <v>0.05881057268722467</v>
       </c>
       <c r="O4">
-        <v>0.9572192513368983</v>
+        <v>0.9888888888888888</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>2.67</v>
       </c>
       <c r="Q4">
-        <v>0.02300771208226221</v>
+        <v>0.05881057268722467</v>
       </c>
       <c r="R4">
-        <v>0.9572192513368983</v>
+        <v>0.9888888888888888</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="V4">
-        <v>0.01889460154241645</v>
+        <v>0.03656387665198238</v>
       </c>
       <c r="W4">
-        <v>0.1375</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="X4">
-        <v>0.09203638565167616</v>
+        <v>0.08213172593331738</v>
       </c>
       <c r="Y4">
-        <v>0.04546361434832386</v>
+        <v>0.1356102095505536</v>
       </c>
       <c r="Z4">
-        <v>0.5585957666494579</v>
+        <v>0.6184832011407183</v>
       </c>
       <c r="AA4">
-        <v>0.1388054357420021</v>
+        <v>0.2483395104766798</v>
       </c>
       <c r="AB4">
-        <v>0.09191568630332879</v>
+        <v>0.08199626610317776</v>
       </c>
       <c r="AC4">
-        <v>0.04688974943867331</v>
+        <v>0.166343244373502</v>
       </c>
       <c r="AD4">
-        <v>0.291</v>
+        <v>0.192</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.291</v>
+        <v>0.192</v>
       </c>
       <c r="AG4">
-        <v>-1.179</v>
+        <v>-1.468</v>
       </c>
       <c r="AH4">
-        <v>0.0037264217387407</v>
+        <v>0.004211265134234077</v>
       </c>
       <c r="AI4">
-        <v>0.02292963517453313</v>
+        <v>0.01466544454628781</v>
       </c>
       <c r="AJ4">
-        <v>-0.01538742642356534</v>
+        <v>-0.03341527815715196</v>
       </c>
       <c r="AK4">
-        <v>-0.1050708493004189</v>
+        <v>-0.1284114765570329</v>
       </c>
       <c r="AL4">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="AM4">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="AN4">
-        <v>0.1682080924855491</v>
+        <v>0.05565217391304347</v>
       </c>
       <c r="AO4">
-        <v>93.68421052631579</v>
+        <v>233.3333333333333</v>
       </c>
       <c r="AP4">
-        <v>-0.6815028901734105</v>
+        <v>-0.4255072463768116</v>
       </c>
       <c r="AQ4">
-        <v>93.68421052631579</v>
+        <v>233.3333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASN Broker Public Company Limited (SET:ASN)</t>
+          <t>Thai Group Holdings Public Company Limited (SET:TGH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,122 +989,113 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.00635</v>
-      </c>
-      <c r="E5">
-        <v>0.0664</v>
-      </c>
       <c r="G5">
-        <v>0.2101736972704714</v>
+        <v>0.1875384300061488</v>
       </c>
       <c r="H5">
-        <v>0.2101736972704714</v>
+        <v>0.1875384300061488</v>
       </c>
       <c r="I5">
-        <v>0.1555831265508685</v>
+        <v>0.03981022036161123</v>
       </c>
       <c r="J5">
-        <v>0.1235513063786308</v>
+        <v>0.02529607752144047</v>
       </c>
       <c r="K5">
-        <v>0.378</v>
+        <v>1.12</v>
       </c>
       <c r="L5">
-        <v>0.09379652605459056</v>
+        <v>0.002295552367288379</v>
       </c>
       <c r="M5">
-        <v>0.397</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02294797687861272</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.05026455026455</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.397</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02294797687861272</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>1.05026455026455</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V5">
-        <v>0.1433526011560693</v>
+        <v>0.2008978675645342</v>
       </c>
       <c r="W5">
-        <v>0.04242424242424243</v>
+        <v>0.005123513266239708</v>
       </c>
       <c r="X5">
-        <v>0.1055243251428911</v>
+        <v>0.13296916873363</v>
       </c>
       <c r="Y5">
-        <v>-0.06310008271864873</v>
+        <v>-0.1278456554673902</v>
       </c>
       <c r="Z5">
-        <v>0.4507829977628636</v>
+        <v>0.7723077662209551</v>
       </c>
       <c r="AA5">
-        <v>0.05569482826687722</v>
+        <v>0.0195363571247358</v>
       </c>
       <c r="AB5">
-        <v>0.09436587538103888</v>
+        <v>0.08349281648378155</v>
       </c>
       <c r="AC5">
-        <v>-0.03867104711416166</v>
+        <v>-0.06395645935904576</v>
       </c>
       <c r="AD5">
-        <v>5.56</v>
+        <v>525.7</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.2429674278494302</v>
       </c>
       <c r="AF5">
-        <v>5.56</v>
+        <v>525.9429674278495</v>
       </c>
       <c r="AG5">
-        <v>3.08</v>
+        <v>454.3429674278494</v>
       </c>
       <c r="AH5">
-        <v>0.2432195975503062</v>
+        <v>0.5960754342056414</v>
       </c>
       <c r="AI5">
-        <v>0.4152352501867064</v>
+        <v>0.7032799535934547</v>
       </c>
       <c r="AJ5">
-        <v>0.1511285574092247</v>
+        <v>0.5604032173961261</v>
       </c>
       <c r="AK5">
-        <v>0.2823098075160403</v>
+        <v>0.6718635007118574</v>
       </c>
       <c r="AL5">
-        <v>0.15</v>
+        <v>17.4</v>
       </c>
       <c r="AM5">
-        <v>0.15</v>
+        <v>17.4</v>
       </c>
       <c r="AN5">
-        <v>7.192755498059507</v>
+        <v>7.513005202080834</v>
       </c>
       <c r="AO5">
-        <v>4.180000000000001</v>
+        <v>1.109195402298851</v>
       </c>
       <c r="AP5">
-        <v>3.984476067270375</v>
+        <v>6.493211104839785</v>
       </c>
       <c r="AQ5">
-        <v>4.180000000000001</v>
+        <v>1.109195402298851</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KWI Public Company Limited (SET:KWI)</t>
+          <t>ASN Broker Public Company Limited (SET:ASN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,115 +1115,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.216</v>
+        <v>0.0375</v>
       </c>
       <c r="G6">
-        <v>-0.4658634538152611</v>
+        <v>0.1901601830663615</v>
       </c>
       <c r="H6">
-        <v>-0.4658634538152611</v>
+        <v>0.1901601830663615</v>
       </c>
       <c r="I6">
-        <v>-0.07126948518430253</v>
+        <v>0.09313501144164758</v>
       </c>
       <c r="J6">
-        <v>-0.07126948518430253</v>
+        <v>0.04656750572082379</v>
       </c>
       <c r="K6">
-        <v>-3.65</v>
+        <v>-0.023</v>
       </c>
       <c r="L6">
-        <v>-0.1465863453815261</v>
+        <v>-0.005263157894736842</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.137</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.01317307692307692</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-5.956521739130435</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.137</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.01317307692307692</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-5.956521739130435</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>12.1</v>
+        <v>0.749</v>
       </c>
       <c r="V6">
-        <v>0.07254196642685851</v>
+        <v>0.07201923076923077</v>
       </c>
       <c r="W6">
-        <v>-0.07005758157389635</v>
+        <v>-0.002937420178799489</v>
       </c>
       <c r="X6">
-        <v>0.119072634378464</v>
+        <v>0.1007879713442776</v>
       </c>
       <c r="Y6">
-        <v>-0.1891302159523604</v>
+        <v>-0.1037253915230771</v>
       </c>
       <c r="Z6">
-        <v>0.144491856486338</v>
+        <v>0.4005499541704858</v>
       </c>
       <c r="AA6">
-        <v>-0.01029786022510543</v>
+        <v>0.01865261228230981</v>
       </c>
       <c r="AB6">
-        <v>0.09587177459967181</v>
+        <v>0.08451539701377044</v>
       </c>
       <c r="AC6">
-        <v>-0.1061696348247772</v>
+        <v>-0.06586278473146062</v>
       </c>
       <c r="AD6">
-        <v>106.1</v>
+        <v>5.66</v>
       </c>
       <c r="AE6">
-        <v>0.7280509054456642</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>106.8280509054457</v>
+        <v>5.66</v>
       </c>
       <c r="AG6">
-        <v>94.72805090544567</v>
+        <v>4.911</v>
       </c>
       <c r="AH6">
-        <v>0.3904133752075036</v>
+        <v>0.3524283935242839</v>
       </c>
       <c r="AI6">
-        <v>0.5980474531516533</v>
+        <v>0.4167893961708395</v>
       </c>
       <c r="AJ6">
-        <v>0.3622099066524003</v>
+        <v>0.3207497877343087</v>
       </c>
       <c r="AK6">
-        <v>0.5688414077411624</v>
+        <v>0.3827449146598083</v>
       </c>
       <c r="AL6">
-        <v>3.73</v>
+        <v>0.334</v>
       </c>
       <c r="AM6">
-        <v>3.73</v>
+        <v>0.334</v>
       </c>
       <c r="AN6">
-        <v>-67.62268961121734</v>
+        <v>8.167388167388168</v>
       </c>
       <c r="AO6">
-        <v>-0.5844504021447722</v>
+        <v>1.218562874251497</v>
       </c>
       <c r="AP6">
-        <v>-60.3747934387799</v>
+        <v>7.086580086580088</v>
       </c>
       <c r="AQ6">
-        <v>-0.5844504021447722</v>
+        <v>1.218562874251497</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thai Group Holdings Public Company Limited (SET:TGH)</t>
+          <t>KWI Public Company Limited (SET:KWI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1239,23 +1245,26 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.357</v>
+      </c>
       <c r="G7">
-        <v>-0.448589626933576</v>
+        <v>-0.2161094224924012</v>
       </c>
       <c r="H7">
-        <v>-0.448589626933576</v>
+        <v>-0.2161094224924012</v>
       </c>
       <c r="I7">
-        <v>-0.04815796499596636</v>
+        <v>-0.4576605292690888</v>
       </c>
       <c r="J7">
-        <v>-0.04815796499596636</v>
+        <v>-0.4576605292690888</v>
       </c>
       <c r="K7">
-        <v>-36.9</v>
+        <v>-21.7</v>
       </c>
       <c r="L7">
-        <v>-0.06715195632393084</v>
+        <v>-0.6595744680851063</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1279,73 +1288,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>64.3</v>
+        <v>16.8</v>
       </c>
       <c r="V7">
-        <v>0.1463026166097838</v>
+        <v>0.5508196721311476</v>
       </c>
       <c r="W7">
-        <v>-0.101123595505618</v>
+        <v>-0.3131313131313131</v>
       </c>
       <c r="X7">
-        <v>0.1380297052209613</v>
+        <v>0.2071249726600467</v>
       </c>
       <c r="Y7">
-        <v>-0.2391533007265792</v>
+        <v>-0.5202562857913599</v>
       </c>
       <c r="Z7">
-        <v>0.8268205742184497</v>
+        <v>0.2235431621487735</v>
       </c>
       <c r="AA7">
-        <v>-0.0398179962711569</v>
+        <v>-0.1023068819034934</v>
       </c>
       <c r="AB7">
-        <v>0.09399768240568446</v>
+        <v>0.08761076347032543</v>
       </c>
       <c r="AC7">
-        <v>-0.1338156786768414</v>
+        <v>-0.1899176453738188</v>
       </c>
       <c r="AD7">
-        <v>477.2</v>
+        <v>109.9</v>
       </c>
       <c r="AE7">
-        <v>0.4940088264175815</v>
+        <v>0.5751570647651003</v>
       </c>
       <c r="AF7">
-        <v>477.6940088264176</v>
+        <v>110.4751570647651</v>
       </c>
       <c r="AG7">
-        <v>413.3940088264176</v>
+        <v>93.6751570647651</v>
       </c>
       <c r="AH7">
-        <v>0.5208211177018526</v>
+        <v>0.7836498243021071</v>
       </c>
       <c r="AI7">
-        <v>0.6796103008816312</v>
+        <v>0.6786978987267029</v>
       </c>
       <c r="AJ7">
-        <v>0.4846956416017599</v>
+        <v>0.7543792114223593</v>
       </c>
       <c r="AK7">
-        <v>0.6473502775043826</v>
+        <v>0.6417198580112098</v>
       </c>
       <c r="AL7">
-        <v>12.9</v>
+        <v>3.73</v>
       </c>
       <c r="AM7">
-        <v>12.9</v>
+        <v>3.73</v>
       </c>
       <c r="AN7">
-        <v>21.65547286258849</v>
+        <v>-7.609749342196372</v>
       </c>
       <c r="AO7">
-        <v>-2.069767441860465</v>
+        <v>-4.128686327077748</v>
       </c>
       <c r="AP7">
-        <v>18.75993868335531</v>
+        <v>-6.486300863091338</v>
       </c>
       <c r="AQ7">
-        <v>-2.069767441860465</v>
+        <v>-4.128686327077748</v>
       </c>
     </row>
   </sheetData>
